--- a/output/pdf_financials_xlsx/BGF.xlsx
+++ b/output/pdf_financials_xlsx/BGF.xlsx
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.255489</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1626,19 +1626,19 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.075137</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.822636</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.21613</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.10867</v>
       </c>
     </row>
     <row r="35">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.255489</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -1692,19 +1692,19 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.075137</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.822636</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.21613</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.10867</v>
       </c>
     </row>
     <row r="37">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.284994</v>
+        <v>0.029505</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -2088,19 +2088,19 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.235281</v>
+        <v>0.160144</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.889749</v>
+        <v>0.06711300000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.539821</v>
+        <v>0.036821</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.244431</v>
+        <v>0.028301</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.205722</v>
+        <v>0.097052</v>
       </c>
     </row>
     <row r="49">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/BGF.xlsx
+++ b/output/pdf_financials_xlsx/BGF.xlsx
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.0009389999999999999</v>
+        <v>0.022993</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -629,19 +629,19 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.001739</v>
+        <v>0.050203</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.005218</v>
+        <v>0.048627</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.002399</v>
+        <v>0.048121</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.002286</v>
+        <v>0.041885</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.002101</v>
+        <v>0.041184</v>
       </c>
     </row>
     <row r="8">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.0009389999999999999</v>
+        <v>0.022993</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.001739</v>
+        <v>0.050203</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.005218</v>
+        <v>0.048627</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.002399</v>
+        <v>0.048121</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.002286</v>
+        <v>0.041885</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.002101</v>
+        <v>0.041184</v>
       </c>
     </row>
     <row r="11">
@@ -11892,7 +11892,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
